--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -77,7 +77,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -283,7 +283,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -489,7 +489,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -695,7 +695,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -901,7 +901,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Date Worked 1 back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
+          <t>The master workbook matches on this column to pull Claim Status, Notes, Processed Date and Latest Date Worked back from this file with INDEX/MATCH, so you can freely sort or filter these rows without breaking the link. Do not edit it.</t>
         </r>
       </text>
     </comment>
@@ -2085,19 +2085,19 @@
     <t>Cells you edit</t>
   </si>
   <si>
-    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Date Worked 1 (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
+    <t>Four columns are shaded pale yellow and are the ones meant to be edited here: Claim Status (A), Notes (B), Processed Date (C) and Latest Date Worked (K). Claim Status has a drop-down of the statuses already in use - it is a suggestion, not a restriction, so you can type anything.</t>
   </si>
   <si>
     <t>Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected.</t>
   </si>
   <si>
-    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
-  </si>
-  <si>
-    <t>Processed Date and Date Worked 1</t>
-  </si>
-  <si>
-    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Date Worked 1 starts empty.</t>
+    <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Latest Date Worked: "08/12/2026".</t>
+  </si>
+  <si>
+    <t>Processed Date and Latest Date Worked</t>
+  </si>
+  <si>
+    <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Latest Date Worked starts empty.</t>
   </si>
   <si>
     <t>Processed Date is filled in wherever the row had something to fill it with: the date written into the Notes where there was one, otherwise the Insurance Check Date. A date from the Notes is never overwritten by a check date. Where the row has neither, it is blank for you to fill in.</t>

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="352">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2125,6 +2125,15 @@
   </si>
   <si>
     <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -4720,7 +4729,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A9" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5720,10 +5729,10 @@
     </row>
     <row r="9" spans="1:41">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>349</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>151</v>
+        <v>350</v>
       </c>
       <c r="C9" s="3">
         <v>46227</v>
@@ -6222,7 +6231,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A12" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7080,7 +7089,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A6" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8483,7 +8492,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A11" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9323,7 +9332,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Claim Status" prompt="Pick a status, or type a new one." sqref="A2:A6" xr:uid="{00000000-0002-0000-0400-000000000000}">
-      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected"</formula1>
+      <formula1>"Denied,Finalized,PAID,Pending,Received,Rejected,Under Review"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9436,7 +9445,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="9" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="30">

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -1078,7 +1078,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="353">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2134,6 +2134,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540 days</t>
   </si>
 </sst>
 </file>
@@ -3780,16 +3783,16 @@
         <v>46183</v>
       </c>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L9" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>-134</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:N9" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
-        <v>183</v>
+        <f ca="1">IF($F2="","",$F2+90-TODAY())</f>
+        <v>-137</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>183</v>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
+        <v>180</v>
       </c>
       <c r="O2" s="6">
         <v>46146</v>
@@ -3801,10 +3804,10 @@
         <v>48</v>
       </c>
       <c r="R2" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T2" s="5" t="s">
         <v>49</v>
@@ -3894,16 +3897,16 @@
         <v>46183</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>-128</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>233</v>
+        <f ca="1">IF($F3="","",$F3+90-TODAY())</f>
+        <v>-131</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>233</v>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
+        <v>230</v>
       </c>
       <c r="O3" s="6">
         <v>46152</v>
@@ -3915,10 +3918,10 @@
         <v>48</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T3" s="5" t="s">
         <v>49</v>
@@ -4004,16 +4007,16 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>-125</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>204</v>
+        <f ca="1">IF($F4="","",$F4+90-TODAY())</f>
+        <v>-128</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>204</v>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
+        <v>201</v>
       </c>
       <c r="O4" s="6">
         <v>46155</v>
@@ -4025,10 +4028,10 @@
         <v>48</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T4" s="5" t="s">
         <v>49</v>
@@ -4120,15 +4123,15 @@
         <v>46142</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-124</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="O5" s="6">
@@ -4234,15 +4237,15 @@
         <v>46142</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-120</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="O6" s="6">
@@ -4350,16 +4353,16 @@
         <v>46183</v>
       </c>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-119</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-122</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>186</v>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
+        <v>183</v>
       </c>
       <c r="O7" s="6">
         <v>46161</v>
@@ -4371,10 +4374,10 @@
         <v>48</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>49</v>
@@ -4464,15 +4467,15 @@
         <v>46266</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-117</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="O8" s="6">
@@ -4578,15 +4581,15 @@
         <v>46247</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-117</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="O9" s="6">
@@ -4938,15 +4941,15 @@
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L12" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>148</v>
       </c>
       <c r="M2" s="12">
-        <f t="shared" ref="M2:M9" ca="1" si="1">IF($C2="","",$C2+365-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+365-TODAY())</f>
         <v>190</v>
       </c>
       <c r="N2" s="12">
-        <f t="shared" ref="N2:N8" ca="1" si="2">IF($C2="","",$C2+120-TODAY())</f>
+        <f ca="1">IF($C2="","",$C2+120-TODAY())</f>
         <v>-55</v>
       </c>
       <c r="O2" s="6">
@@ -5054,15 +5057,15 @@
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>148</v>
       </c>
       <c r="M3" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C3="","",$C3+365-TODAY())</f>
         <v>218</v>
       </c>
       <c r="N3" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C3="","",$C3+120-TODAY())</f>
         <v>-27</v>
       </c>
       <c r="O3" s="6">
@@ -5168,15 +5171,15 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>151</v>
       </c>
       <c r="M4" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C4="","",$C4+365-TODAY())</f>
         <v>218</v>
       </c>
       <c r="N4" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C4="","",$C4+120-TODAY())</f>
         <v>-27</v>
       </c>
       <c r="O4" s="6">
@@ -5288,15 +5291,15 @@
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>154</v>
       </c>
       <c r="M5" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C5="","",$C5+365-TODAY())</f>
         <v>218</v>
       </c>
       <c r="N5" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C5="","",$C5+120-TODAY())</f>
         <v>-27</v>
       </c>
       <c r="O5" s="6">
@@ -5412,15 +5415,15 @@
         <v>46246</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>154</v>
       </c>
       <c r="M6" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
         <v>206</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
         <v>-39</v>
       </c>
       <c r="O6" s="6">
@@ -5530,15 +5533,15 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>156</v>
       </c>
       <c r="M7" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
         <v>186</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C7="","",$C7+120-TODAY())</f>
         <v>-59</v>
       </c>
       <c r="O7" s="6">
@@ -5644,15 +5647,15 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>161</v>
       </c>
       <c r="M8" s="12">
-        <f t="shared" ca="1" si="1"/>
+        <f ca="1">IF($C8="","",$C8+365-TODAY())</f>
         <v>232</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" ca="1" si="2"/>
+        <f ca="1">IF($C8="","",$C8+120-TODAY())</f>
         <v>-13</v>
       </c>
       <c r="O8" s="6">
@@ -5762,16 +5765,16 @@
         <v>46196</v>
       </c>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-121</v>
       </c>
       <c r="M9" s="12">
-        <f t="shared" ca="1" si="1"/>
-        <v>312</v>
+        <f ca="1">IF($F9="","",$F9+90-TODAY())</f>
+        <v>-124</v>
       </c>
       <c r="N9" s="12">
         <f ca="1">IF($C9="","",$C9+365-TODAY())</f>
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="O9" s="6">
         <v>46159</v>
@@ -5783,10 +5786,10 @@
         <v>48</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T9" s="5" t="s">
         <v>49</v>
@@ -5878,7 +5881,7 @@
         <v>46197</v>
       </c>
       <c r="L10" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
         <v>-118</v>
       </c>
       <c r="M10" s="12">
@@ -5996,7 +5999,7 @@
         <v>46134</v>
       </c>
       <c r="L11" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v/>
       </c>
       <c r="M11" s="12"/>
@@ -6094,7 +6097,7 @@
         <v>46244</v>
       </c>
       <c r="L12" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O12="","",$O12-TODAY())</f>
         <v/>
       </c>
       <c r="M12" s="12"/>
@@ -6934,12 +6937,12 @@
         <v>-121</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>239</v>
+        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
+        <v>-124</v>
       </c>
       <c r="N6" s="12">
         <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O6" s="6">
         <v>46159</v>
@@ -6951,10 +6954,10 @@
         <v>48</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T6" s="5" t="s">
         <v>49</v>
@@ -7296,7 +7299,7 @@
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="12">
-        <f t="shared" ref="L2:L11" ca="1" si="0">IF($O2="","",$O2-TODAY())</f>
+        <f ca="1">IF($O2="","",$O2-TODAY())</f>
         <v>155</v>
       </c>
       <c r="M2" s="12">
@@ -7414,7 +7417,7 @@
         <v>46251</v>
       </c>
       <c r="L3" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O3="","",$O3-TODAY())</f>
         <v>158</v>
       </c>
       <c r="M3" s="12">
@@ -7530,7 +7533,7 @@
         <v>46195</v>
       </c>
       <c r="L4" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O4="","",$O4-TODAY())</f>
         <v>164</v>
       </c>
       <c r="M4" s="12">
@@ -7654,16 +7657,16 @@
         <v>46247</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O5="","",$O5-TODAY())</f>
         <v>-131</v>
       </c>
       <c r="M5" s="12">
         <f ca="1">IF($F5="","",$F5+90-TODAY())</f>
-        <v>-131</v>
+        <v>-134</v>
       </c>
       <c r="N5" s="12">
-        <f ca="1">IF($C5="","",$C5+60-TODAY())</f>
-        <v>-73</v>
+        <f ca="1">IF($C5="","",$C5+540-TODAY())</f>
+        <v>404</v>
       </c>
       <c r="O5" s="6">
         <v>46149</v>
@@ -7681,7 +7684,7 @@
         <v>252</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>253</v>
+        <v>352</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>50</v>
@@ -7768,7 +7771,7 @@
         <v>46192</v>
       </c>
       <c r="L6" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O6="","",$O6-TODAY())</f>
         <v>-118</v>
       </c>
       <c r="M6" s="12">
@@ -7888,16 +7891,16 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O7="","",$O7-TODAY())</f>
         <v>-111</v>
       </c>
       <c r="M7" s="12">
-        <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>297</v>
+        <f ca="1">IF($F7="","",$F7+90-TODAY())</f>
+        <v>-114</v>
       </c>
       <c r="N7" s="12">
         <f ca="1">IF($C7="","",$C7+365-TODAY())</f>
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O7" s="6">
         <v>46169</v>
@@ -7909,10 +7912,10 @@
         <v>48</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>50</v>
+        <v>252</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>49</v>
@@ -8006,7 +8009,7 @@
         <v>46247</v>
       </c>
       <c r="L8" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O8="","",$O8-TODAY())</f>
         <v>-110</v>
       </c>
       <c r="M8" s="12">
@@ -8118,7 +8121,7 @@
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="12">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O9="","",$O9-TODAY())</f>
         <v>-103</v>
       </c>
       <c r="M9" s="12">
@@ -8233,25 +8236,29 @@
       <c r="K10" s="3">
         <v>46195</v>
       </c>
-      <c r="L10" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
+      <c r="L10" s="12">
+        <f ca="1">IF($O10="","",$O10-TODAY())</f>
+        <v>-135</v>
       </c>
       <c r="M10" s="12">
-        <f ca="1">IF($C10="","",$C10+180-TODAY())</f>
-        <v>42</v>
+        <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="N10" s="12">
         <f ca="1">IF($C10="","",$C10+365-TODAY())</f>
-        <v>227</v>
-      </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="5"/>
+        <v>224</v>
+      </c>
+      <c r="O10" s="6">
+        <v>46148</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="Q10" s="5" t="s">
         <v>282</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="S10" s="5" t="s">
         <v>50</v>
@@ -8350,7 +8357,7 @@
         <v>46195</v>
       </c>
       <c r="L11" s="12" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">IF($O11="","",$O11-TODAY())</f>
         <v/>
       </c>
       <c r="M11" s="12"/>
@@ -9174,33 +9181,33 @@
       </c>
       <c r="L6" s="12">
         <f ca="1">IF($O6="","",$O6-TODAY())</f>
-        <v>-125</v>
+        <v>147</v>
       </c>
       <c r="M6" s="12">
-        <f ca="1">IF($F6="","",$F6+90-TODAY())</f>
-        <v>-125</v>
+        <f ca="1">IF($C6="","",$C6+365-TODAY())</f>
+        <v>293</v>
       </c>
       <c r="N6" s="12">
-        <f ca="1">IF($C6="","",$C6+60-TODAY())</f>
-        <v>-9</v>
+        <f ca="1">IF($C6="","",$C6+120-TODAY())</f>
+        <v>48</v>
       </c>
       <c r="O6" s="6">
-        <v>46155</v>
+        <v>46430</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>315</v>
+        <v>99</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>252</v>
+        <v>50</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>50</v>

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -235,20 +235,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -438,20 +424,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -647,20 +619,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -853,20 +811,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -1056,20 +1000,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -3583,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3620,10 +3550,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3744,11 +3673,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -3858,11 +3784,8 @@
       <c r="AN2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>56</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -3972,11 +3895,8 @@
       <c r="AN3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>63</v>
       </c>
@@ -4084,11 +4004,8 @@
       <c r="AN4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>68</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -4198,11 +4115,8 @@
       <c r="AN5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>76</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -4314,11 +4228,8 @@
       <c r="AN6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>80</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -4428,11 +4339,8 @@
       <c r="AN7" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>87</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -4542,11 +4450,8 @@
       <c r="AN8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>90</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -4656,12 +4561,9 @@
       <c r="AN9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>93</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AN9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="L2:L9">
     <cfRule type="expression" dxfId="99" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -4742,7 +4644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AO12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4780,10 +4682,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -4904,11 +4805,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -5020,11 +4918,8 @@
       <c r="AN2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>107</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -5134,11 +5029,8 @@
       <c r="AN3" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -5254,11 +5146,8 @@
       <c r="AN4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>118</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -5376,11 +5265,8 @@
       <c r="AN5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>127</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>128</v>
       </c>
@@ -5496,11 +5382,8 @@
       <c r="AN6" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>136</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -5610,11 +5493,8 @@
       <c r="AN7" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>144</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -5726,11 +5606,8 @@
       <c r="AN8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>150</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2" t="s">
         <v>349</v>
       </c>
@@ -5842,11 +5719,8 @@
       <c r="AN9" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>158</v>
-      </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:40">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -5960,11 +5834,8 @@
       <c r="AN10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>166</v>
-      </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:40">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -6058,11 +5929,8 @@
       <c r="AN11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>173</v>
-      </c>
     </row>
-    <row r="12" spans="1:41">
+    <row r="12" spans="1:40">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
@@ -6158,12 +6026,9 @@
       <c r="AN12" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="AO12" s="5" t="s">
-        <v>180</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO12" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AN12" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L12">
     <cfRule type="expression" dxfId="79" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -6244,7 +6109,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -6282,10 +6147,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -6406,11 +6270,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -6528,11 +6389,8 @@
       <c r="AN2" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>196</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>41</v>
       </c>
@@ -6652,11 +6510,8 @@
       <c r="AN3" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>205</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -6770,11 +6625,8 @@
       <c r="AN4" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>212</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -6894,11 +6746,8 @@
       <c r="AN5" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>219</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -7016,12 +6865,9 @@
       <c r="AN6" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>224</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:AN6" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="L2:L6">
     <cfRule type="expression" dxfId="59" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -7102,7 +6948,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7140,10 +6986,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -7264,11 +7109,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
@@ -7378,11 +7220,8 @@
       <c r="AN2" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>231</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>232</v>
       </c>
@@ -7494,11 +7333,8 @@
       <c r="AN3" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>236</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -7618,11 +7454,8 @@
       <c r="AN4" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>246</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -7732,11 +7565,8 @@
       <c r="AN5" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>254</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>63</v>
       </c>
@@ -7854,11 +7684,8 @@
       <c r="AN6" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="7" spans="1:41">
+    <row r="7" spans="1:40">
       <c r="A7" s="2" t="s">
         <v>181</v>
       </c>
@@ -7970,11 +7797,8 @@
       <c r="AN7" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO7" s="5" t="s">
-        <v>265</v>
-      </c>
     </row>
-    <row r="8" spans="1:41">
+    <row r="8" spans="1:40">
       <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
@@ -8086,11 +7910,8 @@
       <c r="AN8" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO8" s="5" t="s">
-        <v>270</v>
-      </c>
     </row>
-    <row r="9" spans="1:41">
+    <row r="9" spans="1:40">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -8198,11 +8019,8 @@
       <c r="AN9" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO9" s="5" t="s">
-        <v>277</v>
-      </c>
     </row>
-    <row r="10" spans="1:41">
+    <row r="10" spans="1:40">
       <c r="A10" s="2" t="s">
         <v>63</v>
       </c>
@@ -8318,11 +8136,8 @@
       <c r="AN10" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO10" s="5" t="s">
-        <v>284</v>
-      </c>
     </row>
-    <row r="11" spans="1:41">
+    <row r="11" spans="1:40">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -8423,12 +8238,9 @@
       <c r="AN11" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="AO11" s="5" t="s">
-        <v>291</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:AN11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <conditionalFormatting sqref="L2:L11">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>
@@ -8509,7 +8321,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -8547,10 +8359,9 @@
     <col min="38" max="38" width="24" customWidth="1"/>
     <col min="39" max="39" width="14" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="30" customHeight="1">
+    <row r="1" spans="1:40" ht="30" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -8671,11 +8482,8 @@
       <c r="AN1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="11" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="2" spans="1:41">
+    <row r="2" spans="1:40">
       <c r="A2" s="2" t="s">
         <v>128</v>
       </c>
@@ -8793,11 +8601,8 @@
       <c r="AN2" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="AO2" s="5" t="s">
-        <v>210</v>
-      </c>
     </row>
-    <row r="3" spans="1:41">
+    <row r="3" spans="1:40">
       <c r="A3" s="2" t="s">
         <v>128</v>
       </c>
@@ -8909,11 +8714,8 @@
       <c r="AN3" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="AO3" s="5" t="s">
-        <v>305</v>
-      </c>
     </row>
-    <row r="4" spans="1:41">
+    <row r="4" spans="1:40">
       <c r="A4" s="2" t="s">
         <v>128</v>
       </c>
@@ -9025,11 +8827,8 @@
       <c r="AN4" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="AO4" s="5" t="s">
-        <v>308</v>
-      </c>
     </row>
-    <row r="5" spans="1:41">
+    <row r="5" spans="1:40">
       <c r="A5" s="2" t="s">
         <v>128</v>
       </c>
@@ -9141,11 +8940,8 @@
       <c r="AN5" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="AO5" s="5" t="s">
-        <v>311</v>
-      </c>
     </row>
-    <row r="6" spans="1:41">
+    <row r="6" spans="1:40">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -9263,12 +9059,9 @@
       <c r="AN6" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="AO6" s="5" t="s">
-        <v>319</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO6" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:AN6" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <conditionalFormatting sqref="L2:L6">
     <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -1008,7 +1008,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="359">
   <si>
     <t>Claim Status</t>
   </si>
@@ -2067,6 +2067,24 @@
   </si>
   <si>
     <t xml:space="preserve">540 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39 claims with a date of service in 2026-02 February, split into one sheet per specialty: BH, DME, GAE, ORTHO, US.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every specialty sheet is sorted by how close the claim is to its primary payer's timely filing deadline. Days Until Deadline (column L) carries the count: claims with five days or less left sit at the top of each sheet in red, a negative number means the filing window has already closed, and a blank means no limit is on file for that payer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order down the sheet, with the colour band each row gets, counted on 19 September 2026:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5 - No limit on file: 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 482 claims for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
   </si>
 </sst>
 </file>
@@ -9161,7 +9179,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="9" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -9174,12 +9192,12 @@
     </row>
     <row r="6" spans="1:1" ht="45">
       <c r="A6" s="9" t="s">
-        <v>323</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="9" t="s">
-        <v>324</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -9194,7 +9212,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="9" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -9204,7 +9222,7 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="9" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -9304,7 +9322,7 @@
     </row>
     <row r="34" spans="1:1" ht="45">
       <c r="A34" s="9" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="30">

--- a/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-02 February - Specialty Claims.xlsx
@@ -1463,7 +1463,7 @@
     <t>796</t>
   </si>
   <si>
-    <t xml:space="preserve">***Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </t>
+    <t xml:space="preserve">Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </t>
   </si>
   <si>
     <t>HF513477727</t>
